--- a/docs/collections/lawlib/metadata/data.xlsx
+++ b/docs/collections/lawlib/metadata/data.xlsx
@@ -1161,7 +1161,7 @@
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>乙7-1493</t>
+          <t>乙:7:1493</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>「三田氏圖書之印」</t>
+          <t>「三宅氏圖書之印」</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">

--- a/docs/collections/lawlib/metadata/data.xlsx
+++ b/docs/collections/lawlib/metadata/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD4"/>
+  <dimension ref="A1:BG4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,260 +439,275 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>書写者／Copier</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>校訂者／Revisor</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>宛先/Recipient</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>宛先原綴</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>差出1/Sender1</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>差出2/Sender2</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>差出3/Sender3</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>差出4/Sender4</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>差出5/Sender5</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>差出6/Sender6</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>差出7/Sender7</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>差出8/Sender8</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>差出9/Sender9</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>差出10/Sender10</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>請求記号/Call No.</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>出版事項/Publication, Discription, etc.Area</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>出版地／Place of Publication</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>数量/Unit</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>日付(和暦)/Japanese Date</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>日付(西暦)/A.D.</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>コレクション4</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>所蔵年次/Year</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>所蔵巻号/Volumes</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>資料区分/Document Categoly</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>種別/Material Type</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>本文言語/Language</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Place</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>備考/Comments</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>署判/Signature</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>内容/Contents</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>納本データ/Note:Legal Deposit Data</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Format</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Identifier</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>形態/Physical Descriptin Area</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>地域/Region</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>印記/Seal</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>iiif viewer</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>ウェブサイトURL</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>アイテムURL</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>利用条件</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>サムネイル</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>機械可読ドキュメント</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>帰属</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>viewingDirection</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>viewingHint</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>コレクション</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>ソート用項目</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>西暦</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>IIIFマニフェストURI</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>IIIF Search API URI</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>アノテーション付きIIIFマニフェストURI</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>Link to TAPAS Project</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>Text with Rich Text Format</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t># of media</t>
         </is>
@@ -721,260 +736,275 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>bibo:producer</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>dcterms:contributor</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>law:atena</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>law:atenaGentetsu</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>law:sashidashinin1</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>law:sashidashinin2</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>law:sashidashinin3</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>law:sashidashinin4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>law:sashidashinin5</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>law:sashidashinin6</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>law:sashidashinin7</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>law:sashidashinin8</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>law:sashidashinin9</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>law:sashidashinin10</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>dcndl:callNumber</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>dcterms:publisher</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>dcndl:publicationPlace</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>dcterms:extent</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>dcterms:date</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>law:ad</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>archiveshub:item</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>dcndl:holdingIssues</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>dcndl:volume</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>dcterms:type</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>dcndl:materialType</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>dcterms:language</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>dcterms:spatial</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>rdfs:comment</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>archiveshub:origination</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>bibo:content</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>dcterms:provenance</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>dcterms:format</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>dcterms:identifier</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>law:physicalDescriptinArea</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>law:region</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>law:seal</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>iiif viewer</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>bibo:identifier</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>dcterms:isPartOf</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>dcterms:relation</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>dcterms:rights</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>foaf:thumbnail</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>rdfs:seeAlso</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>sc:attributionLabel</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>sc:viewingDirection</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>sc:viewingHint</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>uterms:databaseLabel</t>
         </is>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>uterms:sort</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>uterms:year</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>uterms:manifestUri</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>uterms:searchApiUri</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>uterms:annotedManifest</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>uterms:linkToTapas</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>uterms:rtf</t>
         </is>
       </c>
-      <c r="BD2" t="n">
+      <c r="BG2" t="n">
         <v>125</v>
       </c>
     </row>
@@ -999,134 +1029,137 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
         <is>
           <t>NB::247</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Leonhard Simion Nf</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
         <is>
           <t>6冊</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr">
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
         <is>
           <t>1921-1922</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr">
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>1921-1922</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Nr. 1-6, 3. Jahrg.</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>雑誌;Serials</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr">
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>ドイツ語</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>ドイツ連邦共和国</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr">
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>jpeg</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>3000001573</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a1a320db-682a-4846-b99f-9414f6a17a2c.json</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>a1a320db-682a-4846-b99f-9414f6a17a2c</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/lawlib/</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/lawlib/document/a1a320db-682a-4846-b99f-9414f6a17a2c</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="AT3" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/dced11b359a295c948d42c7ac5db74cb0a0ac167.jpg</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22146</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>東京大学法学部研究室図書室 Graduate Schools for Law and Politics / Faculty of Law Library, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>東京大学法学部研究室図書室所蔵コレクション</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0001</t>
-        </is>
-      </c>
+      <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="inlineStr">
         <is>
+          <t>東京大学法学部研究室図書室所蔵コレクション</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr">
+        <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a1a320db-682a-4846-b99f-9414f6a17a2c/manifest</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="n">
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="n">
         <v>56</v>
       </c>
     </row>
@@ -1159,134 +1192,137 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>乙:7:1493</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
+          <t>乙:7:1493</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>[文久3年]</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>[1863]</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>和古書</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>日本語</t>
-        </is>
-      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr">
+        <is>
           <t>裏表紙:墨書: 「御取締役 鵜殿鳩翁」</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr">
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr">
         <is>
           <t>冊子</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>「三宅氏圖書之印」</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/427554b3-6a83-44a5-a5eb-d611db3b5e67.json</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>427554b3-6a83-44a5-a5eb-d611db3b5e67</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/lawlib</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/lawlib/document/427554b3-6a83-44a5-a5eb-d611db3b5e67</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr">
+      <c r="AT4" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/69c784fec663d539755d7f1845f8046946190044.jpg</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AU4" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1253830</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>東京大学法学部研究室図書室 Graduate Schools for Law and Politics / Faculty of Law Library, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>東京大学法学部研究室図書室所蔵コレクション</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>0002</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="inlineStr">
         <is>
+          <t>東京大学法学部研究室図書室所蔵コレクション</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr">
+        <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/427554b3-6a83-44a5-a5eb-d611db3b5e67/manifest</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="n">
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="n">
         <v>69</v>
       </c>
     </row>

--- a/docs/collections/lawlib/metadata/data.xlsx
+++ b/docs/collections/lawlib/metadata/data.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/lawlib/</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/law</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/lawlib/document/a1a320db-682a-4846-b99f-9414f6a17a2c</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/law/document/a1a320db-682a-4846-b99f-9414f6a17a2c</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1134,14 +1134,18 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>東京大学法学部研究室図書室 Graduate Schools for Law and Politics / Faculty of Law Library, The University of Tokyo, JAPAN</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr"/>
+          <t>東京大学法学部研究室図書室法制史資料室 Legal History Section, Faculty of Law Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
       <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>東京大学法学部研究室図書室所蔵コレクション</t>
+          <t>東京大学法学部法制史資料室所蔵コレクション</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
